--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11945.18</v>
+        <v>11987.81</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10030.3</v>
+        <v>10063.29</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16650.57</v>
+        <v>16765.18</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>57762.43</v>
+        <v>58160.02</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17672.59</v>
+        <v>18185.92</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>27373.62</v>
+        <v>27738.04</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>69664.99000000001</v>
+        <v>69953.73</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8675.540000000001</v>
+        <v>8505.719999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19515.96</v>
+        <v>19557.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2385-1050-CM25</t>
+          <t>4291-15-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11987.81</v>
+        <v>52874.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1220203-115-CM25</t>
+          <t>1375735-8-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10063.29</v>
+        <v>24653.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1495202-3-SE25</t>
+          <t>1233623-86-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,62 +676,58 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16765.18</v>
+        <v>5890.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2429-3187-CM25</t>
+          <t>2385-405-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.616.370-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -756,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>58160.02</v>
+        <v>8934.530000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1261592-167-CM26</t>
+          <t>2383-4-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -817,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18185.92</v>
+        <v>49989.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1113265-32-CM26</t>
+          <t>2383-5-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IMPORTADORA PROMSA SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.780.759-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>27738.04</v>
+        <v>11884.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1261592-377-SE26</t>
+          <t>2429-2700-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,32 +920,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>69953.73</v>
+        <v>11677.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2385-473-CM26</t>
+          <t>2385-1050-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -989,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1004,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8505.719999999999</v>
+        <v>11987.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2385-505-CM26</t>
+          <t>1220203-115-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1020,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1050,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1065,7 +1057,564 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>10063.29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1495202-3-SE25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>16765.18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2429-3187-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>58160.02</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1261592-167-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>18185.92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1113265-32-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>62.000.770-6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>27738.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1261592-377-SE26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIAL RENHET SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>69953.73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2385-473-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>8505.719999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2385-505-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>19557.55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4468-104-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>10503.58</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1261592-973-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>46520.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1376,7 +1376,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2385-473-CM26</t>
+          <t>1375735-20-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8505.719999999999</v>
+        <v>37783.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2385-505-CM26</t>
+          <t>2385-473-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>19557.55</v>
+        <v>8505.719999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4468-104-CM26</t>
+          <t>2385-505-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,27 +1508,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10503.58</v>
+        <v>19557.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1261592-973-CM26</t>
+          <t>4468-104-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1614,7 +1614,251 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
+        <v>10503.58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1261592-973-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>46520.53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1410-818-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>17149.16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2384-168-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>22312.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1775-52-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60.804.004-8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>15678.95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1063,7 +1087,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1495202-3-SE25</t>
+          <t>1375735-81-SE25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1097,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1112,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1122,13 +1146,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>16765.18</v>
+        <v>7303.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2429-3187-CM25</t>
+          <t>1495202-3-SE25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1148,17 +1172,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1192,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>58160.02</v>
+        <v>16765.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1261592-167-CM26</t>
+          <t>2429-3187-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,27 +1227,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,28 +1257,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18185.92</v>
+        <v>58160.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1113265-32-CM26</t>
+          <t>1261592-167-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1292,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1307,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,28 +1322,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>27738.04</v>
+        <v>18185.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1261592-377-SE26</t>
+          <t>1113265-32-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1362,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1372,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1387,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1370,13 +1406,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>69953.73</v>
+        <v>27738.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1375735-20-CM26</t>
+          <t>1261592-377-SE26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1422,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,28 +1452,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>37783.66</v>
+        <v>69953.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2385-473-CM26</t>
+          <t>1375735-20-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1447,27 +1487,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,28 +1517,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8505.719999999999</v>
+        <v>37783.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2385-505-CM26</t>
+          <t>2385-473-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,12 +1552,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1538,12 +1582,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1553,13 +1597,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>19557.55</v>
+        <v>8505.719999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4468-104-CM26</t>
+          <t>2385-505-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1569,27 +1613,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1599,28 +1643,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10503.58</v>
+        <v>19557.55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1261592-973-CM26</t>
+          <t>4468-104-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,7 +1683,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1645,12 +1693,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1660,28 +1708,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>46520.53</v>
+        <v>10503.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1410-818-CM26</t>
+          <t>1261592-973-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1691,27 +1743,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,28 +1773,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17149.16</v>
+        <v>46520.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2384-168-CM26</t>
+          <t>1410-818-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1757,22 +1813,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1782,12 +1838,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1797,67 +1853,136 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22312.2</v>
+        <v>17149.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2384-168-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>22312.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>1775-52-CM26</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>60.804.004-8</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>15678.95</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1924,66 +1924,196 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>1261592-1234-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>9647.17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>1775-52-CM26</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>60.804.004-8</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>15678.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>697036-77-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>7626.72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/antofagasta.xlsx
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
